--- a/artfynd/A 31203-2022 artfynd.xlsx
+++ b/artfynd/A 31203-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31203-2022 artfynd.xlsx
+++ b/artfynd/A 31203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104308095</v>
+        <v>104308092</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400476.7632386611</v>
+        <v>400637</v>
       </c>
       <c r="R2" t="n">
-        <v>6719661.280622681</v>
+        <v>6719688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104308090</v>
+        <v>104308085</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400632.6093888343</v>
+        <v>400560</v>
       </c>
       <c r="R3" t="n">
-        <v>6719690.390709462</v>
+        <v>6719765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104308092</v>
+        <v>104308086</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400636.4897342402</v>
+        <v>400669</v>
       </c>
       <c r="R4" t="n">
-        <v>6719688.318020608</v>
+        <v>6719742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104308086</v>
+        <v>104308096</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400668.9647111295</v>
+        <v>400459</v>
       </c>
       <c r="R5" t="n">
-        <v>6719741.475010459</v>
+        <v>6719661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104308093</v>
+        <v>104308097</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400395.5552620532</v>
+        <v>400413</v>
       </c>
       <c r="R6" t="n">
-        <v>6719679.25136943</v>
+        <v>6719661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104308096</v>
+        <v>104308087</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400459.044009638</v>
+        <v>400595</v>
       </c>
       <c r="R7" t="n">
-        <v>6719661.279114753</v>
+        <v>6719709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104308097</v>
+        <v>104308090</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>400412.7854196645</v>
+        <v>400632</v>
       </c>
       <c r="R8" t="n">
-        <v>6719661.575659783</v>
+        <v>6719690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104308087</v>
+        <v>104308093</v>
       </c>
       <c r="B9" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400595.213832712</v>
+        <v>400396</v>
       </c>
       <c r="R9" t="n">
-        <v>6719708.621932526</v>
+        <v>6719679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104308085</v>
+        <v>104308095</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400559.3684025994</v>
+        <v>400477</v>
       </c>
       <c r="R10" t="n">
-        <v>6719765.13901968</v>
+        <v>6719662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104308106</v>
+        <v>104308114</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>400877.7742878575</v>
+        <v>400817</v>
       </c>
       <c r="R11" t="n">
-        <v>6719567.169512209</v>
+        <v>6719535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104308116</v>
+        <v>104308106</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>400426.3731184179</v>
+        <v>400878</v>
       </c>
       <c r="R12" t="n">
-        <v>6719529.993112762</v>
+        <v>6719567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,12 +1745,7 @@
         <v>104308112</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>400429.4871379302</v>
+        <v>400429</v>
       </c>
       <c r="R13" t="n">
-        <v>6719535.804019404</v>
+        <v>6719536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104308119</v>
+        <v>104308115</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>400510.6882818674</v>
+        <v>400427</v>
       </c>
       <c r="R14" t="n">
-        <v>6719499.651120087</v>
+        <v>6719530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104308124</v>
+        <v>104308100</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>400492.6251599776</v>
+        <v>400436</v>
       </c>
       <c r="R15" t="n">
-        <v>6719433.807577809</v>
+        <v>6719599</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104308121</v>
+        <v>104308109</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>400498.4019869012</v>
+        <v>400543</v>
       </c>
       <c r="R16" t="n">
-        <v>6719446.916565672</v>
+        <v>6719545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104308109</v>
+        <v>104308117</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>400543.455114706</v>
+        <v>400590</v>
       </c>
       <c r="R17" t="n">
-        <v>6719545.430671181</v>
+        <v>6719507</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104308120</v>
+        <v>104308119</v>
       </c>
       <c r="B18" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>400501.2955207337</v>
+        <v>400511</v>
       </c>
       <c r="R18" t="n">
-        <v>6719462.562337057</v>
+        <v>6719500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104308115</v>
+        <v>104308121</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>400426.3731184179</v>
+        <v>400499</v>
       </c>
       <c r="R19" t="n">
-        <v>6719529.993112762</v>
+        <v>6719447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104308113</v>
+        <v>104308124</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>400429.4871379302</v>
+        <v>400493</v>
       </c>
       <c r="R20" t="n">
-        <v>6719535.804019404</v>
+        <v>6719434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104308104</v>
+        <v>104308125</v>
       </c>
       <c r="B21" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>400458.0892331452</v>
+        <v>400636</v>
       </c>
       <c r="R21" t="n">
-        <v>6719573.343549464</v>
+        <v>6719424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,19 +2586,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104308110</v>
+        <v>104308104</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>400424.2398661994</v>
+        <v>400458</v>
       </c>
       <c r="R22" t="n">
-        <v>6719541.846169719</v>
+        <v>6719573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,19 +2683,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104308103</v>
+        <v>104308120</v>
       </c>
       <c r="B23" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>400403.0715614581</v>
+        <v>400501</v>
       </c>
       <c r="R23" t="n">
-        <v>6719577.322244718</v>
+        <v>6719463</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,19 +2780,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104308117</v>
+        <v>104308118</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>400589.6412348803</v>
+        <v>400442</v>
       </c>
       <c r="R24" t="n">
-        <v>6719506.807216685</v>
+        <v>6719504</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,19 +2877,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104308107</v>
+        <v>104308102</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>400395.2185419527</v>
+        <v>400401</v>
       </c>
       <c r="R25" t="n">
-        <v>6719560.339988856</v>
+        <v>6719578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3324,19 +2974,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104308100</v>
+        <v>104308105</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>400435.6655371095</v>
+        <v>400458</v>
       </c>
       <c r="R26" t="n">
-        <v>6719599.025633657</v>
+        <v>6719573</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3436,19 +3071,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104308118</v>
+        <v>104308110</v>
       </c>
       <c r="B27" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6450</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>400441.8977865502</v>
+        <v>400424</v>
       </c>
       <c r="R27" t="n">
-        <v>6719504.009854664</v>
+        <v>6719542</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3548,19 +3168,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104308125</v>
+        <v>104308107</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>400635.6058690508</v>
+        <v>400395</v>
       </c>
       <c r="R28" t="n">
-        <v>6719424.452909853</v>
+        <v>6719561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,19 +3265,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104308105</v>
+        <v>104308113</v>
       </c>
       <c r="B29" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>400458.0892331452</v>
+        <v>400429</v>
       </c>
       <c r="R29" t="n">
-        <v>6719573.343549464</v>
+        <v>6719536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3772,19 +3362,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104308126</v>
+        <v>104308116</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>400216.7161002717</v>
+        <v>400427</v>
       </c>
       <c r="R30" t="n">
-        <v>6719371.168155127</v>
+        <v>6719530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,19 +3459,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104308127</v>
+        <v>104308103</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>400175.1170763847</v>
+        <v>400403</v>
       </c>
       <c r="R31" t="n">
-        <v>6719326.616765409</v>
+        <v>6719578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3996,19 +3556,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,19 +3585,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104308128</v>
+        <v>104308126</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4075,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>399877.4817308244</v>
+        <v>400216</v>
       </c>
       <c r="R32" t="n">
-        <v>6719315.223068031</v>
+        <v>6719371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,19 +3653,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104308130</v>
+        <v>104308127</v>
       </c>
       <c r="B33" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>399885.6250751372</v>
+        <v>400175</v>
       </c>
       <c r="R33" t="n">
-        <v>6719307.133359341</v>
+        <v>6719327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4220,19 +3750,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104308123</v>
+        <v>104308130</v>
       </c>
       <c r="B34" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>400253.5702951755</v>
+        <v>399885</v>
       </c>
       <c r="R34" t="n">
-        <v>6719439.931182304</v>
+        <v>6719307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4332,19 +3847,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,19 +3876,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104308133</v>
+        <v>104308128</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4411,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>400220.8902574539</v>
+        <v>399877</v>
       </c>
       <c r="R35" t="n">
-        <v>6719184.299262061</v>
+        <v>6719315</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4444,19 +3944,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,32 +3973,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104308088</v>
+        <v>104308131</v>
       </c>
       <c r="B36" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4523,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>400362.2175606661</v>
+        <v>399786</v>
       </c>
       <c r="R36" t="n">
-        <v>6719701.795438586</v>
+        <v>6719302</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4556,19 +4041,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,16 +4073,11 @@
         <v>104308101</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4635,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>400333.6523803301</v>
+        <v>400334</v>
       </c>
       <c r="R37" t="n">
-        <v>6719594.477175567</v>
+        <v>6719595</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,19 +4138,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,19 +4167,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104308111</v>
+        <v>104308108</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4747,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400278.3832324275</v>
+        <v>400350</v>
       </c>
       <c r="R38" t="n">
-        <v>6719536.054909565</v>
+        <v>6719560</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4780,19 +4235,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,37 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104308099</v>
+        <v>104308111</v>
       </c>
       <c r="B39" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>400291.7763373411</v>
+        <v>400279</v>
       </c>
       <c r="R39" t="n">
-        <v>6719610.870463889</v>
+        <v>6719536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4892,19 +4332,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4934,16 +4364,11 @@
         <v>104308132</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4971,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>400190.2107087412</v>
+        <v>400190</v>
       </c>
       <c r="R40" t="n">
-        <v>6719231.838784898</v>
+        <v>6719232</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5004,19 +4429,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,37 +4458,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104308089</v>
+        <v>104308133</v>
       </c>
       <c r="B41" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5083,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>400362.2175606661</v>
+        <v>400221</v>
       </c>
       <c r="R41" t="n">
-        <v>6719701.795438586</v>
+        <v>6719185</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5116,19 +4526,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,15 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104308098</v>
+        <v>104308094</v>
       </c>
       <c r="B42" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5195,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>400305.8013424787</v>
+        <v>400354</v>
       </c>
       <c r="R42" t="n">
-        <v>6719655.200078285</v>
+        <v>6719665</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5228,19 +4623,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,15 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104308108</v>
+        <v>104308098</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,21 +4663,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5307,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>400350.406960882</v>
+        <v>400306</v>
       </c>
       <c r="R43" t="n">
-        <v>6719559.614393064</v>
+        <v>6719655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5340,19 +4720,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,15 +4749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104308094</v>
+        <v>104308123</v>
       </c>
       <c r="B44" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5395,21 +4760,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>400353.8073549976</v>
+        <v>400254</v>
       </c>
       <c r="R44" t="n">
-        <v>6719664.681853161</v>
+        <v>6719440</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5452,19 +4817,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5488,6 +4843,297 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>104308089</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kattstjärtsvadet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>400362</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6719702</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>104308088</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kattstjärtsvadet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>400362</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6719702</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>104308099</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kattstjärtsvadet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>400292</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6719611</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31203-2022 artfynd.xlsx
+++ b/artfynd/A 31203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308085</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308087</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308090</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308093</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308095</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308114</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308112</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308115</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308109</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308117</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308119</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308121</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308124</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308125</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308104</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308120</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308118</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308102</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308105</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308110</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308107</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308113</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308116</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308103</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308126</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308127</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308130</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308128</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308131</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308101</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308108</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308111</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308132</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308133</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308094</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308098</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308123</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308089</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308088</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,8 +5364,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308099</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>